--- a/output/pdf_financials_xlsx/PEX.xlsx
+++ b/output/pdf_financials_xlsx/PEX.xlsx
@@ -6052,13 +6052,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.752729</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.011887</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>7.152039</v>
       </c>
     </row>
     <row r="93">
@@ -10026,7 +10026,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11135,7 +11139,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PEX.xlsx
+++ b/output/pdf_financials_xlsx/PEX.xlsx
@@ -2429,34 +2429,34 @@
         <v>0.127897</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.489304</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.694374</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.598401</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.213872</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.89532</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.549391</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.813084</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.54184</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.012095</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.194173</v>
       </c>
     </row>
     <row r="35">
@@ -2545,34 +2545,34 @@
         <v>0.159912</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.114105</v>
+        <v>0.603409</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.010936</v>
+        <v>0.683438</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.598401</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.213872</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.89532</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.054</v>
+        <v>0.603391</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.044833</v>
+        <v>7.857917</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.54184</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.012095</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.194173</v>
       </c>
     </row>
     <row r="37">
@@ -3241,10 +3241,10 @@
         <v>0.002</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.493954</v>
+        <v>0.00465</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.70996</v>
+        <v>0.015586</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.5100980000000001</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.060885</v>
+        <v>0.04879</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.253625</v>
+        <v>0.059452</v>
       </c>
     </row>
     <row r="49">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">

--- a/output/pdf_financials_xlsx/PEX.xlsx
+++ b/output/pdf_financials_xlsx/PEX.xlsx
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.032015</v>
@@ -2539,7 +2539,7 @@
         <v>0.59421</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.151606</v>
+        <v>0.277606</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.159912</v>
@@ -3235,7 +3235,7 @@
         <v>0.015</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.128</v>
+        <v>0.002</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.002</v>
@@ -3530,13 +3530,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.010496</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.03862</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.027034</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0.018922</v>
@@ -5776,22 +5776,22 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>33.346072</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>34.021981</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>34.021981</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>42.620478</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>42.667978</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>42.963593</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>43.066428</v>
@@ -20528,7 +20528,11 @@
           <t>Marketable securities Note 4</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -20827,7 +20831,11 @@
           <t>Share capital Note 6</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -21419,7 +21427,11 @@
           <t>Equipment Note 4</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -22219,7 +22231,11 @@
           <t>Equipment Note 4 38,620</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22619,7 +22635,11 @@
           <t>Share capital Note 6 42,620,478</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -23720,7 +23740,11 @@
           <t>Capital stock Note 7</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>33.346072</v>
       </c>
